--- a/解题-gpt/结果/问题四_2批次_修复版.xlsx
+++ b/解题-gpt/结果/问题四_2批次_修复版.xlsx
@@ -542,34 +542,34 @@
         <v>2100</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>132.0721581834358</v>
+        <v>103.1152421386595</v>
       </c>
       <c r="G2" t="n">
-        <v>8.375285829114478</v>
+        <v>7.562048201282888</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
         <v>2</v>
@@ -603,16 +603,16 @@
         <v>1322</v>
       </c>
       <c r="D3" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E3" t="n">
         <v>65</v>
       </c>
       <c r="F3" t="n">
-        <v>205.6147938843214</v>
+        <v>171.5840041697735</v>
       </c>
       <c r="G3" t="n">
-        <v>97.90737742768306</v>
+        <v>86.29191385608814</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
@@ -636,10 +636,10 @@
         <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
@@ -793,22 +793,22 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
